--- a/samagam result data/class 12/secondary_marks_Monthly_Test_XII-Sept__Mathematics (1).xlsx
+++ b/samagam result data/class 12/secondary_marks_Monthly_Test_XII-Sept__Mathematics (1).xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/samagam result data/class 12/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_349AD7C86AB5C5729D54306ED7E157AA4C902F98" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141CF390-E709-4313-80D4-EC8A3E6BDD02}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Marks" sheetId="1" r:id="rId4"/>
+    <sheet name="Marks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Roll No</t>
   </si>
@@ -104,23 +109,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -147,14 +144,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -444,14 +449,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -479,7 +485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -493,7 +499,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5</v>
       </c>
@@ -507,7 +513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>7</v>
       </c>
@@ -521,7 +527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>11</v>
       </c>
@@ -535,7 +541,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>12</v>
       </c>
@@ -549,7 +555,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>13</v>
       </c>
@@ -563,7 +569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>14</v>
       </c>
@@ -577,7 +583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>18</v>
       </c>
@@ -591,7 +597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>19</v>
       </c>
@@ -605,7 +611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20</v>
       </c>
@@ -619,7 +625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>24</v>
       </c>
@@ -633,7 +639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>25</v>
       </c>
@@ -647,7 +653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>26</v>
       </c>
@@ -661,7 +667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>27</v>
       </c>
@@ -675,7 +681,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>28</v>
       </c>
@@ -689,7 +695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>30</v>
       </c>
@@ -703,7 +709,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>31</v>
       </c>
@@ -717,7 +723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
@@ -731,7 +737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>33</v>
       </c>
@@ -745,7 +751,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>35</v>
       </c>
@@ -759,7 +765,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>36</v>
       </c>
@@ -773,7 +779,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>37</v>
       </c>
@@ -788,8 +794,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>